--- a/stories/arbres/ATOM-LAN.SON.001-03.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hanna s'assoit sous l'auvent. Papa est là. Maman arrose les pots. Il pleut. Ça fait plic ploc. Papa dit : c'est un son. Quel nom ? Hanna dit : la pluie. Papa dit : oui. Le nom du son, c'est la pluie. Plus loin, un bruit long. Tchou tchou. Papa dit : encore un son. Quel nom ? Hanna dit : le train. Papa dit : oui. Le nom du son, c'est le train. Puis, près des fleurs, un miaulement. Miaou. Maman dit : un son. Quel nom ? Hanna dit : le chat. Le chat vient. Hanna le caresse. Pluie. Train. Chat. On entend. On nomme le son.</t>
+          <t>Hanna s'assoit sous l'auvent. Papa est là. Maman arrose les pots. Il pleut. Ça fait plic ploc. C'est un son. Quel nom ? La pluie. Oui. Le nom du son, c'est la pluie. Plus loin, un bruit long. Tchou tchou. Encore un son. Quel nom ? Le train. Oui. Le nom du son, c'est le train. Puis, près des fleurs, un miaulement. Miaou. Un son. Quel nom ? Le chat. Le chat vient. Hanna le caresse. Pluie. Train. Chat. On entend. On nomme le son.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,22 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hanna s'assoit sous l'auvent. Papa est là. Maman arrose les pots. Il pleut. Ça fait plic ploc.
+papa|C'est un son. Quel nom ?
+enfant-f|La pluie.
+papa|Oui.
+narrateur|Le nom du son, c'est la pluie. Plus loin, un bruit long. Tchou tchou.
+papa|Encore un son. Quel nom ?
+enfant-f|Le train.
+papa|Oui.
+narrateur|Le nom du son, c'est le train. Puis, près des fleurs, un miaulement. Miaou.
+maman|Un son. Quel nom ?
+enfant-f|Le chat.
+narrateur|Le chat vient. Hanna le caresse. Pluie. Train. Chat. On entend. On nomme le son.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1497,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Hanna entend un bruit. C'est quoi ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1670,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hanna a entendu un son. Elle a dit le nom. Pluie. Train. Chat.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1833,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat ronronne. Hanna pose la tête sur papa.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +2000,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2040,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.SON.001-03.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1321,6 +1326,7 @@
 narrateur|Le chat vient. Hanna le caresse. Pluie. Train. Chat. On entend. On nomme le son.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1504,6 +1510,7 @@
           <t>narrateur|Hanna entend un bruit. C'est quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1675,6 +1682,7 @@
           <t>narrateur|Hanna a entendu un son. Elle a dit le nom. Pluie. Train. Chat.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1838,6 +1846,7 @@
           <t>narrateur|Le chat ronronne. Hanna pose la tête sur papa.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2005,6 +2014,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2023,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2047,6 +2057,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2248,6 +2272,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-LAN.SON.001-03.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hanna nomme la pluie</t>
+          <t>Les pots luisent, Amir écoute</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sous l'auvent, les pots luisent. Amir écoute la pluie, le train, le chat. Papa et maman l'aident à dire le nom.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hanna s'assoit sous l'auvent. Papa est là. Maman arrose les pots. Il pleut. Ça fait plic ploc. C'est un son. Quel nom ? La pluie. Oui. Le nom du son, c'est la pluie. Plus loin, un bruit long. Tchou tchou. Encore un son. Quel nom ? Le train. Oui. Le nom du son, c'est le train. Puis, près des fleurs, un miaulement. Miaou. Un son. Quel nom ? Le chat. Le chat vient. Hanna le caresse. Pluie. Train. Chat. On entend. On nomme le son.</t>
+          <t>Sous l'auvent, le sol est froid. Les pots de fleurs luisent. Une goutte tombe d'une feuille. La terre sent fort. Maman arrose les pots. Papa s'assoit sur le banc. Le bois du banc est un peu rêche. Une goutte d'eau brille, puis plus. Les bottes d'Amir sont encore sèches. Viens sous l'auvent, Amir. Le banc est sec. Oui, papa. Les pots sont mouillés. J'arrose encore un peu. En ce moment, Amir s'assoit. Il pleut. Ça fait plic ploc. C'est un son. Quel nom ? La pluie. Oui. Le nom du son, c'est la pluie. Plus loin, un bruit long. Tchou tchou. Encore un son. Quel nom ? Le train. Oui. Le nom du son, c'est le train. Puis, près des fleurs, un miaulement. Miaou. Un son. Quel nom ? Le chat. Oui. Le chat vient. Amir le caresse. Le poil est humide. Pluie. Train. Chat. On entend. On nomme le son. Bravo, Amir. C'est du bon travail. Tu as dit le nom. Tu restes sur le banc ? Oui, papa. Une autre goutte tombe. Plic. Encore la pluie. La pluie. Tu as nommé le son. Le chat se frotte au pot.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,18 +1324,60 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Hanna s'assoit sous l'auvent. Papa est là. Maman arrose les pots. Il pleut. Ça fait plic ploc.
-papa|C'est un son. Quel nom ?
-enfant-f|La pluie.
+          <t>narrateur|Sous l'auvent, le sol est froid.
+narrateur|Les pots de fleurs luisent.
+narrateur|Une goutte tombe d'une feuille.
+narrateur|La terre sent fort.
+narrateur|Maman arrose les pots.
+narrateur|Papa s'assoit sur le banc.
+narrateur|Le bois du banc est un peu rêche.
+narrateur|Une goutte d'eau brille, puis plus.
+narrateur|Les bottes d'Amir sont encore sèches.
+papa|Viens sous l'auvent, Amir.
+papa|Le banc est sec.
+enfant-m|Oui, papa.
+maman|Les pots sont mouillés.
+maman|J'arrose encore un peu.
+narrateur|En ce moment, Amir s'assoit.
+narrateur|Il pleut.
+narrateur|Ça fait plic ploc.
+papa|C'est un son.
+papa|Quel nom ?
+enfant-m|La pluie.
 papa|Oui.
-narrateur|Le nom du son, c'est la pluie. Plus loin, un bruit long. Tchou tchou.
-papa|Encore un son. Quel nom ?
-enfant-f|Le train.
+papa|Le nom du son, c'est la pluie.
+narrateur|Plus loin, un bruit long.
+narrateur|Tchou tchou.
+papa|Encore un son.
+papa|Quel nom ?
+enfant-m|Le train.
 papa|Oui.
-narrateur|Le nom du son, c'est le train. Puis, près des fleurs, un miaulement. Miaou.
-maman|Un son. Quel nom ?
-enfant-f|Le chat.
-narrateur|Le chat vient. Hanna le caresse. Pluie. Train. Chat. On entend. On nomme le son.</t>
+papa|Le nom du son, c'est le train.
+narrateur|Puis, près des fleurs, un miaulement.
+narrateur|Miaou.
+maman|Un son.
+maman|Quel nom ?
+enfant-m|Le chat.
+maman|Oui.
+narrateur|Le chat vient.
+narrateur|Amir le caresse.
+narrateur|Le poil est humide.
+papa|Pluie.
+maman|Train.
+enfant-m|Chat.
+papa|On entend.
+papa|On nomme le son.
+maman|Bravo, Amir.
+maman|C'est du bon travail.
+papa|Tu as dit le nom.
+papa|Tu restes sur le banc ?
+enfant-m|Oui, papa.
+narrateur|Une autre goutte tombe.
+narrateur|Plic.
+maman|Encore la pluie.
+enfant-m|La pluie.
+papa|Tu as nommé le son.
+narrateur|Le chat se frotte au pot.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1351,7 +1405,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Hanna entend un bruit. C'est quoi ?</t>
+          <t>Amir entend un bruit. C'est quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1507,7 +1561,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Hanna entend un bruit. C'est quoi ?</t>
+          <t>narrateur|Amir entend un bruit.
+narrateur|C'est quoi ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1535,7 +1590,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hanna a entendu un son. Elle a dit le nom. Pluie. Train. Chat.</t>
+          <t>Amir a entendu un son. Il a dit le nom. Pluie. Train. Chat. Bravo. Tu as nommé le son. Le chat est là. Oui. C'est du bon travail, Amir.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1679,7 +1734,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hanna a entendu un son. Elle a dit le nom. Pluie. Train. Chat.</t>
+          <t>narrateur|Amir a entendu un son.
+narrateur|Il a dit le nom.
+papa|Pluie.
+papa|Train.
+papa|Chat.
+maman|Bravo.
+maman|Tu as nommé le son.
+enfant-m|Le chat est là.
+papa|Oui.
+papa|C'est du bon travail, Amir.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1707,7 +1771,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le chat ronronne. Hanna pose la tête sur papa.</t>
+          <t>Le chat ronronne. Amir pose la tête sur papa. Tu es au chaud, là. Oui. Les pots ont assez d'eau. On rentre bientôt ? Encore un peu. D'accord. Une goutte tombe encore. Plic. Le banc reste sec sous l'auvent. Tu as dit le nom. On écoute encore un peu.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1843,7 +1907,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le chat ronronne. Hanna pose la tête sur papa.</t>
+          <t>narrateur|Le chat ronronne.
+narrateur|Amir pose la tête sur papa.
+papa|Tu es au chaud, là.
+enfant-m|Oui.
+maman|Les pots ont assez d'eau.
+maman|On rentre bientôt ?
+enfant-m|Encore un peu.
+papa|D'accord.
+narrateur|Une goutte tombe encore.
+narrateur|Plic.
+narrateur|Le banc reste sec sous l'auvent.
+maman|Tu as dit le nom.
+papa|On écoute encore un peu.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1871,7 +1947,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai entendu un son. J'ai dit le nom. Bravo, Amir. Tu as fait du bon travail. Les pots luisent encore. Une feuille goutte, tout doucement. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2011,7 +2087,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai entendu un son.
+enfant-m|J'ai dit le nom.
+papa|Bravo, Amir.
+maman|Tu as fait du bon travail.
+narrateur|Les pots luisent encore.
+narrateur|Une feuille goutte, tout doucement.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2033,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2071,6 +2153,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.SON.001-03.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-03.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sous l'auvent, le sol est froid. Les pots de fleurs luisent. Une goutte tombe d'une feuille. La terre sent fort. Maman arrose les pots. Papa s'assoit sur le banc. Le bois du banc est un peu rêche. Une goutte d'eau brille, puis plus. Les bottes d'Amir sont encore sèches. Viens sous l'auvent, Amir. Le banc est sec. Oui, papa. Les pots sont mouillés. J'arrose encore un peu. En ce moment, Amir s'assoit. Il pleut. Ça fait plic ploc. C'est un son. Quel nom ? La pluie. Oui. Le nom du son, c'est la pluie. Plus loin, un bruit long. Tchou tchou. Encore un son. Quel nom ? Le train. Oui. Le nom du son, c'est le train. Puis, près des fleurs, un miaulement. Miaou. Un son. Quel nom ? Le chat. Oui. Le chat vient. Amir le caresse. Le poil est humide. Pluie. Train. Chat. On entend. On nomme le son. Bravo, Amir. C'est du bon travail. Tu as dit le nom. Tu restes sur le banc ? Oui, papa. Une autre goutte tombe. Plic. Encore la pluie. La pluie. Tu as nommé le son. Le chat se frotte au pot.</t>
+          <t>Sous l'auvent, le sol est froid. Les pots de fleurs luisent. Une goutte tombe d'une feuille. La terre sent fort. Maman arrose les pots. Papa s'assoit sur le banc. Le bois du banc est un peu rêche. Une goutte d'eau brille, puis plus. Les bottes d'Amir sont encore sèches. Viens sous l'auvent, Amir. Le banc est sec. Oui, papa. Les pots sont mouillés. J'arrose encore un peu. En ce moment, Amir s'assoit. Il pleut. Ça fait plic ploc. C'est un son. Quel nom ? La pluie. Oui. Le nom du son, c'est la pluie. Plus loin, un bruit long. Tchou tchou. Encore un son. Quel nom ? Le train. Oui. Le nom du son, c'est le train. Puis, près des fleurs, un miaulement. Miaou. Un son. Quel nom ? Le chat. Oui. Le chat vient. Amir le caresse. Le poil est humide. Pluie. Train. Chat. On entend. On nomme le son. Bravo, Amir. Tu as dit le nom. Tu restes sur le banc ? Oui, papa. Une autre goutte tombe. Plic. Encore la pluie. La pluie. Tu as nommé le son. Le chat se frotte au pot.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hanna s'assoit sous l'auvent. Papa est là. Maman arrose les pots. Il pleut. Ça fait plic ploc. Papa dit : c'est un &lt;emphasis level="moderate"&gt;son&lt;/emphasis&gt;. Quel nom ? Hanna dit : la pluie. Papa dit : oui. Le nom du son, c'est la pluie. Plus loin, un bruit long. Tchou tchou. Papa dit : encore un son. Quel nom ? Hanna dit : le train. Papa dit : oui. Le nom du son, c'est le train. Puis, près des fleurs, un miaulement. Miaou. Maman dit : un son. Quel nom ? Hanna dit : le chat. Le chat vient. Hanna le caresse. Pluie. Train. Chat. On entend. On nomme le son.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sous l'auvent, le sol est froid. Les pots de fleurs luisent. Une goutte tombe d'une feuille. La terre sent fort. Maman arrose les pots. Papa s'assoit sur le banc. Le bois du banc est un peu rêche. Une goutte d'eau brille, puis plus. Les bottes d'Amir sont encore sèches. Viens sous l'auvent, Amir. Le banc est sec. Oui, papa. Les pots sont mouillés. J'arrose encore un peu. En ce moment, Amir s'assoit. Il pleut. Ça fait plic ploc. C'est un son. Quel nom ? La pluie. Oui. Le nom du son, c'est la pluie. Plus loin, un bruit long. Tchou tchou. Encore un son. Quel nom ? Le train. Oui. Le nom du son, c'est le train. Puis, près des fleurs, un miaulement. Miaou. Un son. Quel nom ? Le chat. Oui. Le chat vient. Amir le caresse. Le poil est humide. Pluie. Train. Chat. On entend. On nomme le son. Bravo, Amir. Tu as dit le nom. Tu restes sur le banc ? Oui, papa. Une autre goutte tombe. Plic. Encore la pluie. La pluie. Tu as nommé le son. Le chat se frotte au pot.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1368,7 +1368,6 @@
 papa|On entend.
 papa|On nomme le son.
 maman|Bravo, Amir.
-maman|C'est du bon travail.
 papa|Tu as dit le nom.
 papa|Tu restes sur le banc ?
 enfant-m|Oui, papa.
@@ -1380,7 +1379,6 @@
 narrateur|Le chat se frotte au pot.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1410,7 +1408,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hanna entend un bruit. C'est quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir entend un bruit. C'est quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1565,7 +1563,6 @@
 narrateur|C'est quoi ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1590,12 +1587,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amir a entendu un son. Il a dit le nom. Pluie. Train. Chat. Bravo. Tu as nommé le son. Le chat est là. Oui. C'est du bon travail, Amir.</t>
+          <t>Amir a entendu un son. Il a dit le nom. Pluie. Train. Chat. Bravo. Tu as nommé le son. Le chat est là. Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hanna a entendu un &lt;emphasis level="moderate"&gt;son&lt;/emphasis&gt;. Elle a dit le nom. Pluie. Train. Chat.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a entendu un son. Il a dit le nom. Pluie. Train. Chat. Bravo. Tu as nommé le son. Le chat est là. Oui.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1742,11 +1739,9 @@
 maman|Bravo.
 maman|Tu as nommé le son.
 enfant-m|Le chat est là.
-papa|Oui.
-papa|C'est du bon travail, Amir.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+papa|Oui.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1776,7 +1771,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le chat ronronne. Hanna pose la tête sur papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le chat ronronne. Amir pose la tête sur papa. Tu es au chaud, là. Oui. Les pots ont assez d'eau. On rentre bientôt ? Encore un peu. D'accord. Une goutte tombe encore. Plic. Le banc reste sec sous l'auvent. Tu as dit le nom. On écoute encore un peu.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1922,7 +1917,6 @@
 papa|On écoute encore un peu.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1947,12 +1941,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai entendu un son. J'ai dit le nom. Bravo, Amir. Tu as fait du bon travail. Les pots luisent encore. Une feuille goutte, tout doucement. L'histoire est finie.</t>
+          <t>J'ai entendu un son. J'ai dit le nom. Bravo, Amir. Les pots luisent encore. Une feuille goutte, tout doucement.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai entendu un son. J'ai dit le nom. Bravo, Amir. Les pots luisent encore. Une feuille goutte, tout doucement.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2090,13 +2084,10 @@
           <t>enfant-m|J'ai entendu un son.
 enfant-m|J'ai dit le nom.
 papa|Bravo, Amir.
-maman|Tu as fait du bon travail.
 narrateur|Les pots luisent encore.
-narrateur|Une feuille goutte, tout doucement.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Une feuille goutte, tout doucement.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2115,7 +2106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2160,6 +2151,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.SON.001-03.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-03.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hanna, papa, maman</t>
+          <t>Amir, papa, maman</t>
         </is>
       </c>
     </row>
